--- a/从零开始学Slots/从零开始学Slots-30-番外篇-Python模拟LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-30-番外篇-Python模拟LineSlots.xlsx
@@ -9239,6 +9239,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N310" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9782,5 +9785,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N64" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-30-番外篇-Python模拟LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-30-番外篇-Python模拟LineSlots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="310">
   <si>
     <r>
       <rPr>
@@ -7410,7 +7410,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7537,6 +7537,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9382,8 +9390,8 @@
       <c r="A13" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>252</v>
+      <c r="B13" s="32">
+        <v>3</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>253</v>
@@ -9598,8 +9606,8 @@
       <c r="D30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>283</v>
+      <c r="A31" s="33">
+        <v>1</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>284</v>
@@ -9611,8 +9619,8 @@
       <c r="E31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>286</v>
+      <c r="A32" s="33">
+        <v>2</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>287</v>
@@ -9625,8 +9633,8 @@
       <c r="F32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>289</v>
+      <c r="A33" s="33">
+        <v>3</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>290</v>
@@ -9638,8 +9646,8 @@
       <c r="E33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
-        <v>292</v>
+      <c r="A34" s="33">
+        <v>4</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>293</v>
@@ -9651,8 +9659,8 @@
       <c r="E34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>295</v>
+      <c r="A35" s="33">
+        <v>5</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>296</v>

--- a/从零开始学Slots/从零开始学Slots-30-番外篇-Python模拟LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-30-番外篇-Python模拟LineSlots.xlsx
@@ -7221,12 +7221,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -7410,7 +7411,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7544,6 +7545,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9520,11 +9529,11 @@
       <c r="A24" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="34" t="n">
         <f aca="false">B14/10000</f>
         <v>0.8</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="35" t="n">
         <f aca="false">B24^3</f>
         <v>0.512</v>
       </c>
@@ -9540,11 +9549,11 @@
       <c r="A25" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="34" t="n">
         <f aca="false">B15/10000</f>
         <v>0.2</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="35" t="n">
         <f aca="false">B25^3</f>
         <v>0.008</v>
       </c>
